--- a/frontend/src/pruebas/fixtures/importacion.xlsx
+++ b/frontend/src/pruebas/fixtures/importacion.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -437,7 +437,7 @@
         <v>1750000</v>
       </c>
       <c r="F2" s="1" t="d">
-        <v>2026-01-14T19:00:00.000Z</v>
+        <v>2026-01-15T00:00:00.000Z</v>
       </c>
     </row>
     <row r="3">
@@ -457,12 +457,32 @@
         <v>2000000</v>
       </c>
       <c r="F3" s="1" t="d">
-        <v>2025-11-30T19:00:00.000Z</v>
+        <v>2025-12-01T00:00:00.000Z</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Luz</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Peña</v>
+      </c>
+      <c r="C5" t="str">
+        <v>9988776655</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Cajera</v>
+      </c>
+      <c r="E5">
+        <v>1500000</v>
+      </c>
+      <c r="F5" s="1" t="d">
+        <v>2026-02-02T00:00:00.000Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F5"/>
   </ignoredErrors>
 </worksheet>
 </file>